--- a/config/generated/templates/StandardProfile.xlsx
+++ b/config/generated/templates/StandardProfile.xlsx
@@ -34,16 +34,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>08d0c6c1f548f093</t>
+    <t>e39b156cc1b3099b</t>
   </si>
   <si>
     <t>#name</t>
@@ -91,7 +91,7 @@
     <t>enum&lt;WaveTransitionPolicy&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
